--- a/artfynd/A 55855-2025 artfynd.xlsx
+++ b/artfynd/A 55855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129744274</v>
       </c>
       <c r="B2" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129744461</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129744495</v>
       </c>
       <c r="B4" t="n">
-        <v>88986</v>
+        <v>88987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129744535</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129744656</v>
+        <v>129744424</v>
       </c>
       <c r="B6" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462185</v>
+        <v>462232</v>
       </c>
       <c r="R6" t="n">
-        <v>6871328</v>
+        <v>6871349</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129744424</v>
+        <v>129744656</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462232</v>
+        <v>462185</v>
       </c>
       <c r="R7" t="n">
-        <v>6871349</v>
+        <v>6871328</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 55855-2025 artfynd.xlsx
+++ b/artfynd/A 55855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129744274</v>
       </c>
       <c r="B2" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129744461</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129744495</v>
       </c>
       <c r="B4" t="n">
-        <v>88987</v>
+        <v>88992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129744535</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129744424</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129744656</v>
       </c>
       <c r="B7" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55855-2025 artfynd.xlsx
+++ b/artfynd/A 55855-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129744424</v>
+        <v>129744656</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462232</v>
+        <v>462185</v>
       </c>
       <c r="R6" t="n">
-        <v>6871349</v>
+        <v>6871328</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129744656</v>
+        <v>129744424</v>
       </c>
       <c r="B7" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462185</v>
+        <v>462232</v>
       </c>
       <c r="R7" t="n">
-        <v>6871328</v>
+        <v>6871349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 55855-2025 artfynd.xlsx
+++ b/artfynd/A 55855-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129744656</v>
+        <v>129744424</v>
       </c>
       <c r="B6" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462185</v>
+        <v>462232</v>
       </c>
       <c r="R6" t="n">
-        <v>6871328</v>
+        <v>6871349</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129744424</v>
+        <v>129744656</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462232</v>
+        <v>462185</v>
       </c>
       <c r="R7" t="n">
-        <v>6871349</v>
+        <v>6871328</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 55855-2025 artfynd.xlsx
+++ b/artfynd/A 55855-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129744495</v>
       </c>
       <c r="B4" t="n">
-        <v>88992</v>
+        <v>88996</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129744424</v>
+        <v>129744656</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462232</v>
+        <v>462185</v>
       </c>
       <c r="R6" t="n">
-        <v>6871349</v>
+        <v>6871328</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129744656</v>
+        <v>129744424</v>
       </c>
       <c r="B7" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462185</v>
+        <v>462232</v>
       </c>
       <c r="R7" t="n">
-        <v>6871328</v>
+        <v>6871349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 55855-2025 artfynd.xlsx
+++ b/artfynd/A 55855-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129744495</v>
       </c>
       <c r="B4" t="n">
-        <v>88996</v>
+        <v>88998</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129744656</v>
+        <v>129744424</v>
       </c>
       <c r="B6" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462185</v>
+        <v>462232</v>
       </c>
       <c r="R6" t="n">
-        <v>6871328</v>
+        <v>6871349</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129744424</v>
+        <v>129744656</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462232</v>
+        <v>462185</v>
       </c>
       <c r="R7" t="n">
-        <v>6871349</v>
+        <v>6871328</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 55855-2025 artfynd.xlsx
+++ b/artfynd/A 55855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129744274</v>
       </c>
       <c r="B2" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129744461</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129744495</v>
       </c>
       <c r="B4" t="n">
-        <v>88998</v>
+        <v>89001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129744535</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129744424</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129744656</v>
       </c>
       <c r="B7" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55855-2025 artfynd.xlsx
+++ b/artfynd/A 55855-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129744424</v>
+        <v>129744656</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462232</v>
+        <v>462185</v>
       </c>
       <c r="R6" t="n">
-        <v>6871349</v>
+        <v>6871328</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129744656</v>
+        <v>129744424</v>
       </c>
       <c r="B7" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462185</v>
+        <v>462232</v>
       </c>
       <c r="R7" t="n">
-        <v>6871328</v>
+        <v>6871349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 55855-2025 artfynd.xlsx
+++ b/artfynd/A 55855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129744274</v>
       </c>
       <c r="B2" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129744461</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129744495</v>
       </c>
       <c r="B4" t="n">
-        <v>89001</v>
+        <v>89004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129744535</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129744656</v>
+        <v>129744424</v>
       </c>
       <c r="B6" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462185</v>
+        <v>462232</v>
       </c>
       <c r="R6" t="n">
-        <v>6871328</v>
+        <v>6871349</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129744424</v>
+        <v>129744656</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462232</v>
+        <v>462185</v>
       </c>
       <c r="R7" t="n">
-        <v>6871349</v>
+        <v>6871328</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 55855-2025 artfynd.xlsx
+++ b/artfynd/A 55855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129744274</v>
       </c>
       <c r="B2" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129744461</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129744495</v>
       </c>
       <c r="B4" t="n">
-        <v>89004</v>
+        <v>89005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129744535</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129744424</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129744656</v>
       </c>
       <c r="B7" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55855-2025 artfynd.xlsx
+++ b/artfynd/A 55855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129744274</v>
       </c>
       <c r="B2" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129744461</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129744495</v>
       </c>
       <c r="B4" t="n">
-        <v>89005</v>
+        <v>89022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129744535</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129744424</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129744656</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
